--- a/data/trans_dic/Q25_A_R3-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Q25_A_R3-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar hace menos tiempo (3.374 años)</t>
+          <t>Población que dejo de fumar hace menos tiempo (3.374 años) (tasa de respuesta: 96,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,43; 33,77</t>
+          <t>15,75; 33,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,57; 31,21</t>
+          <t>14,97; 31,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,23; 32,57</t>
+          <t>14,15; 31,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,89; 26,72</t>
+          <t>8,52; 25,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,96; 46,93</t>
+          <t>18,7; 50,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,17; 54,9</t>
+          <t>24,39; 51,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,54; 37,29</t>
+          <t>17,23; 38,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,18; 33,15</t>
+          <t>15,01; 33,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,2; 34,79</t>
+          <t>18,68; 33,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,76; 34,5</t>
+          <t>20,47; 34,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,77; 31,31</t>
+          <t>17,63; 31,9</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,86; 25,98</t>
+          <t>13,57; 26,24</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,19; 42,2</t>
+          <t>20,67; 42,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,81; 36,34</t>
+          <t>18,27; 37,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,73; 33,08</t>
+          <t>14,64; 32,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,65; 25,11</t>
+          <t>9,79; 23,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,65; 53,84</t>
+          <t>24,14; 54,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,29; 50,15</t>
+          <t>23,59; 49,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,22; 40,05</t>
+          <t>18,09; 38,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,07; 42,42</t>
+          <t>19,89; 41,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,75; 42,61</t>
+          <t>25,11; 42,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,51; 38,63</t>
+          <t>22,67; 38,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,59; 32,82</t>
+          <t>18,01; 32,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,26; 28,12</t>
+          <t>15,89; 28,13</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,56; 25,86</t>
+          <t>10,56; 25,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,14; 33,23</t>
+          <t>19,07; 32,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,31; 33,02</t>
+          <t>17,05; 32,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,98; 93,08</t>
+          <t>9,35; 93,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,63; 62,52</t>
+          <t>23,52; 65,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,56; 47,78</t>
+          <t>14,39; 47,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,29; 59,1</t>
+          <t>15,48; 60,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,83; 41,66</t>
+          <t>9,66; 43,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,26; 29,84</t>
+          <t>15,08; 29,53</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,75; 33,15</t>
+          <t>20,24; 33,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,65; 34,0</t>
+          <t>17,79; 33,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,84; 92,89</t>
+          <t>11,6; 93,1</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,88; 26,98</t>
+          <t>16,41; 26,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,54; 36,09</t>
+          <t>25,46; 36,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,62; 31,81</t>
+          <t>20,56; 32,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,19; 19,72</t>
+          <t>10,05; 19,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,67; 51,87</t>
+          <t>28,02; 52,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,65; 49,43</t>
+          <t>29,68; 49,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,32; 43,7</t>
+          <t>23,92; 42,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,08; 41,71</t>
+          <t>22,64; 42,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,46; 29,86</t>
+          <t>20,6; 30,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,19; 37,38</t>
+          <t>28,29; 37,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23,49; 32,86</t>
+          <t>23,75; 33,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,97; 24,08</t>
+          <t>15,21; 24,48</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,42; 42,78</t>
+          <t>19,64; 43,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,92; 29,16</t>
+          <t>14,39; 29,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,03; 24,29</t>
+          <t>11,08; 24,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,09; 26,72</t>
+          <t>9,9; 25,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,81; 59,94</t>
+          <t>28,95; 61,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,63; 45,72</t>
+          <t>22,5; 44,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,31; 42,26</t>
+          <t>20,97; 42,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,61; 39,26</t>
+          <t>20,04; 38,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26,99; 45,67</t>
+          <t>26,99; 45,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,2; 32,01</t>
+          <t>19,59; 32,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,27; 28,57</t>
+          <t>17,19; 28,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,65; 28,15</t>
+          <t>16,83; 29,6</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,27; 100,0</t>
+          <t>34,39; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,95; 100,0</t>
+          <t>30,39; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,6; 100,0</t>
+          <t>17,32; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 87,13</t>
+          <t>0,0; 86,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,78; 48,45</t>
+          <t>18,44; 47,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,1; 52,06</t>
+          <t>26,86; 52,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,2; 56,89</t>
+          <t>27,81; 57,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,74; 32,04</t>
+          <t>8,37; 34,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24,17; 52,04</t>
+          <t>25,2; 52,09</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30,62; 54,24</t>
+          <t>29,24; 53,09</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29,68; 58,42</t>
+          <t>29,18; 56,78</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,85; 37,51</t>
+          <t>11,19; 36,8</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,47; 27,29</t>
+          <t>20,31; 27,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,74; 30,34</t>
+          <t>23,65; 30,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,39; 26,94</t>
+          <t>20,09; 26,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,42; 71,45</t>
+          <t>14,32; 72,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,55; 43,81</t>
+          <t>31,47; 43,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,45; 41,76</t>
+          <t>31,38; 41,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,45; 36,65</t>
+          <t>26,5; 36,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22,39; 31,49</t>
+          <t>22,52; 31,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,09; 30,98</t>
+          <t>25,15; 30,8</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27,09; 32,64</t>
+          <t>27,1; 32,57</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23,75; 29,16</t>
+          <t>23,72; 29,02</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,54; 69,35</t>
+          <t>18,43; 70,12</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar hace menos tiempo (3.374 años)</t>
+          <t>Población que dejo de fumar hace menos tiempo (3.374 años) (tasa de respuesta: 96,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14744; 32262</t>
+          <t>15043; 31840</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16333; 34974</t>
+          <t>16775; 34824</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14420; 33006</t>
+          <t>14338; 31766</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10882; 32713</t>
+          <t>10424; 31683</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7216; 17866</t>
+          <t>7118; 19072</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12847; 29178</t>
+          <t>12962; 27460</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11366; 25628</t>
+          <t>11840; 26720</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10519; 21558</t>
+          <t>9759; 21757</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25651; 46479</t>
+          <t>24958; 44292</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32650; 57000</t>
+          <t>33814; 57488</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30225; 53242</t>
+          <t>29978; 54257</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24110; 48702</t>
+          <t>25441; 49192</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16931; 33711</t>
+          <t>16515; 33942</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16568; 33810</t>
+          <t>16995; 34717</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13319; 28011</t>
+          <t>12396; 27755</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8948; 23285</t>
+          <t>9075; 22096</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9573; 21789</t>
+          <t>9771; 21922</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12365; 26624</t>
+          <t>12526; 26459</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12041; 28009</t>
+          <t>12651; 27117</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11244; 23768</t>
+          <t>11142; 23521</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29787; 51284</t>
+          <t>30224; 51554</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34356; 56443</t>
+          <t>33130; 56114</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28736; 50740</t>
+          <t>27845; 49971</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22696; 41823</t>
+          <t>23630; 41842</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10925; 26764</t>
+          <t>10930; 25901</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31095; 53969</t>
+          <t>30978; 53035</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19922; 38002</t>
+          <t>19625; 37852</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30544; 316512</t>
+          <t>31789; 319471</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5272; 15240</t>
+          <t>5733; 15948</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5119; 16805</t>
+          <t>5060; 16658</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2501; 9669</t>
+          <t>2533; 9872</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2143; 9085</t>
+          <t>2107; 9480</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18228; 38146</t>
+          <t>19278; 37750</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40992; 65496</t>
+          <t>40002; 65838</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24510; 44695</t>
+          <t>23387; 44450</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42853; 336101</t>
+          <t>41992; 336864</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44589; 71243</t>
+          <t>43342; 69875</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>83282; 117672</t>
+          <t>83025; 117400</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54177; 83580</t>
+          <t>54002; 84690</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18980; 36728</t>
+          <t>18713; 36960</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17808; 33380</t>
+          <t>18030; 33980</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33849; 56418</t>
+          <t>33873; 56147</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25551; 44096</t>
+          <t>24136; 42749</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17858; 32272</t>
+          <t>17516; 32751</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>67198; 98064</t>
+          <t>67671; 99603</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>124093; 164560</t>
+          <t>124530; 165303</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>85405; 119492</t>
+          <t>86367; 121154</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>39478; 63476</t>
+          <t>40104; 64544</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12338; 27175</t>
+          <t>12476; 27817</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19137; 37401</t>
+          <t>18459; 37236</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13923; 30653</t>
+          <t>13979; 31079</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8619; 22816</t>
+          <t>8457; 21657</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11338; 22794</t>
+          <t>11010; 23480</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15943; 32206</t>
+          <t>15850; 31020</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17090; 33884</t>
+          <t>16813; 34343</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13671; 27367</t>
+          <t>13970; 27175</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27406; 46381</t>
+          <t>27406; 46368</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38140; 63603</t>
+          <t>38919; 63705</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35648; 58961</t>
+          <t>35490; 59615</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25829; 43662</t>
+          <t>26101; 45912</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1839; 5527</t>
+          <t>1901; 5527</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>960; 6016</t>
+          <t>1828; 6016</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>980; 5570</t>
+          <t>965; 5570</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 6080</t>
+          <t>0; 6064</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8539; 20920</t>
+          <t>7959; 20647</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15819; 32807</t>
+          <t>16923; 32945</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12305; 25734</t>
+          <t>12581; 26012</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2837; 11746</t>
+          <t>3069; 12715</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11772; 25345</t>
+          <t>12272; 25369</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21134; 37444</t>
+          <t>20187; 36647</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15078; 29682</t>
+          <t>14824; 28846</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5173; 16371</t>
+          <t>4885; 16059</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>125287; 167006</t>
+          <t>124325; 166548</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>196522; 251189</t>
+          <t>195806; 249507</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>141854; 187411</t>
+          <t>139744; 186942</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>120232; 595719</t>
+          <t>119389; 603474</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>78394; 108845</t>
+          <t>78185; 108434</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>122332; 162450</t>
+          <t>122091; 160725</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>104659; 139770</t>
+          <t>101063; 139814</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>73127; 102860</t>
+          <t>73546; 102700</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>215932; 266554</t>
+          <t>216440; 265048</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>329589; 397148</t>
+          <t>329759; 396296</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>255823; 313997</t>
+          <t>255431; 312497</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>215183; 804720</t>
+          <t>213894; 813716</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q25_A_R3-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Q25_A_R3-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,75; 33,33</t>
+          <t>15,12; 33,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,97; 31,07</t>
+          <t>14,91; 30,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,15; 31,35</t>
+          <t>14,32; 32,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,52; 25,88</t>
+          <t>7,95; 24,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,7; 50,1</t>
+          <t>19,0; 48,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,39; 51,67</t>
+          <t>24,97; 52,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,23; 38,88</t>
+          <t>16,68; 37,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,01; 33,46</t>
+          <t>15,06; 31,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,68; 33,15</t>
+          <t>19,35; 34,14</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,47; 34,8</t>
+          <t>20,56; 35,13</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17,63; 31,9</t>
+          <t>17,45; 31,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,57; 26,24</t>
+          <t>12,01; 24,43</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,67; 42,49</t>
+          <t>21,77; 43,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,27; 37,32</t>
+          <t>17,91; 37,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,64; 32,78</t>
+          <t>14,89; 33,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,79; 23,83</t>
+          <t>10,92; 25,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,14; 54,17</t>
+          <t>25,15; 54,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,59; 49,84</t>
+          <t>22,23; 49,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,09; 38,77</t>
+          <t>18,34; 39,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,89; 41,98</t>
+          <t>18,92; 39,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,11; 42,83</t>
+          <t>25,26; 42,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,67; 38,4</t>
+          <t>22,04; 38,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,01; 32,32</t>
+          <t>18,96; 32,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,89; 28,13</t>
+          <t>15,84; 28,34</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,56; 25,03</t>
+          <t>10,27; 25,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,07; 32,65</t>
+          <t>19,16; 33,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,05; 32,89</t>
+          <t>16,25; 31,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,35; 93,95</t>
+          <t>6,34; 18,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,52; 65,42</t>
+          <t>23,47; 63,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,39; 47,37</t>
+          <t>17,78; 48,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,48; 60,34</t>
+          <t>11,1; 58,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,66; 43,47</t>
+          <t>10,15; 44,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,08; 29,53</t>
+          <t>14,54; 28,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,24; 33,32</t>
+          <t>20,52; 33,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,79; 33,82</t>
+          <t>18,56; 33,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,6; 93,1</t>
+          <t>8,77; 20,36</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,41; 26,46</t>
+          <t>16,69; 26,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,46; 36,01</t>
+          <t>25,32; 35,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,56; 32,24</t>
+          <t>20,98; 32,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,05; 19,84</t>
+          <t>10,39; 20,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,02; 52,8</t>
+          <t>28,09; 52,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,68; 49,19</t>
+          <t>29,83; 48,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,92; 42,37</t>
+          <t>23,62; 42,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,64; 42,33</t>
+          <t>22,04; 40,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,6; 30,33</t>
+          <t>20,58; 29,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,29; 37,55</t>
+          <t>28,44; 37,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23,75; 33,32</t>
+          <t>23,18; 32,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,21; 24,48</t>
+          <t>15,06; 24,3</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,64; 43,79</t>
+          <t>19,95; 43,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,39; 29,04</t>
+          <t>15,23; 29,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,08; 24,62</t>
+          <t>10,77; 24,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,9; 25,36</t>
+          <t>10,23; 25,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,95; 61,74</t>
+          <t>29,72; 61,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,5; 44,03</t>
+          <t>21,95; 44,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,97; 42,83</t>
+          <t>20,96; 43,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,04; 38,98</t>
+          <t>21,94; 42,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26,99; 45,66</t>
+          <t>26,16; 45,84</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,59; 32,06</t>
+          <t>19,19; 31,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,19; 28,88</t>
+          <t>16,92; 28,34</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,83; 29,6</t>
+          <t>18,02; 30,09</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34,39; 100,0</t>
+          <t>28,4; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30,39; 100,0</t>
+          <t>16,13; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,32; 100,0</t>
+          <t>17,29; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 86,9</t>
+          <t>0,0; 89,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,44; 47,82</t>
+          <t>20,29; 48,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,86; 52,28</t>
+          <t>26,4; 51,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,81; 57,51</t>
+          <t>27,01; 58,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,37; 34,68</t>
+          <t>10,89; 35,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,2; 52,09</t>
+          <t>25,1; 51,19</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29,24; 53,09</t>
+          <t>29,63; 54,4</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29,18; 56,78</t>
+          <t>29,74; 58,34</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,19; 36,8</t>
+          <t>13,76; 38,63</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>20,31; 27,21</t>
+          <t>20,32; 26,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,65; 30,14</t>
+          <t>23,85; 30,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,09; 26,88</t>
+          <t>20,46; 26,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,32; 72,38</t>
+          <t>12,54; 18,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,47; 43,64</t>
+          <t>31,96; 44,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,38; 41,32</t>
+          <t>31,48; 42,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,5; 36,66</t>
+          <t>26,83; 36,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22,52; 31,44</t>
+          <t>22,84; 31,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,15; 30,8</t>
+          <t>24,74; 30,98</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27,1; 32,57</t>
+          <t>27,01; 32,33</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23,72; 29,02</t>
+          <t>23,75; 29,27</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,43; 70,12</t>
+          <t>17,2; 22,15</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19327</t>
+          <t>19132</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15311</t>
+          <t>15698</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34638</t>
+          <t>34830</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15043; 31840</t>
+          <t>14444; 31954</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16775; 34824</t>
+          <t>16705; 34200</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14338; 31766</t>
+          <t>14510; 32845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10424; 31683</t>
+          <t>10309; 31260</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7118; 19072</t>
+          <t>7233; 18535</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12962; 27460</t>
+          <t>13269; 27837</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11840; 26720</t>
+          <t>11461; 25899</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9759; 21757</t>
+          <t>10453; 21977</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24958; 44292</t>
+          <t>25851; 45616</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33814; 57488</t>
+          <t>33977; 58045</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29978; 54257</t>
+          <t>29670; 54293</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25441; 49192</t>
+          <t>23910; 48653</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>17479</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16708</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31611</t>
+          <t>34984</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16515; 33942</t>
+          <t>17390; 34616</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16995; 34717</t>
+          <t>16661; 34599</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12396; 27755</t>
+          <t>12603; 28234</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9075; 22096</t>
+          <t>11106; 26271</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9771; 21922</t>
+          <t>10178; 22170</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12526; 26459</t>
+          <t>11801; 26334</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12651; 27117</t>
+          <t>12825; 27908</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11142; 23521</t>
+          <t>11744; 24757</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30224; 51554</t>
+          <t>30400; 51079</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33130; 56114</t>
+          <t>32200; 55866</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27845; 49971</t>
+          <t>29315; 50342</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23630; 41842</t>
+          <t>25942; 46406</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>255226</t>
+          <t>12051</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>260316</t>
+          <t>17414</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10930; 25901</t>
+          <t>10629; 25885</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30978; 53035</t>
+          <t>31112; 54355</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19625; 37852</t>
+          <t>18697; 36431</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31789; 319471</t>
+          <t>6697; 19575</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5733; 15948</t>
+          <t>5721; 15380</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5060; 16658</t>
+          <t>6255; 17044</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2533; 9872</t>
+          <t>1817; 9581</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2107; 9480</t>
+          <t>2302; 9984</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19278; 37750</t>
+          <t>18587; 37037</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40002; 65838</t>
+          <t>40541; 66429</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23387; 44450</t>
+          <t>24392; 44085</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>41992; 336864</t>
+          <t>11247; 26114</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26707</t>
+          <t>31375</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>24487</t>
+          <t>25872</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>51194</t>
+          <t>57248</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43342; 69875</t>
+          <t>44068; 70581</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>83025; 117400</t>
+          <t>82559; 116905</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54002; 84690</t>
+          <t>55114; 85696</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18713; 36960</t>
+          <t>21605; 42378</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18030; 33980</t>
+          <t>18078; 33659</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33873; 56147</t>
+          <t>34049; 55489</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24136; 42749</t>
+          <t>23835; 42996</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17516; 32751</t>
+          <t>18363; 33884</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>67671; 99603</t>
+          <t>67605; 98073</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>124530; 165303</t>
+          <t>125187; 166466</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>86367; 121154</t>
+          <t>84285; 118935</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>40104; 64544</t>
+          <t>43859; 70765</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>15700</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19970</t>
+          <t>24552</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>34177</t>
+          <t>40252</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12476; 27817</t>
+          <t>12674; 27434</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18459; 37236</t>
+          <t>19527; 37220</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13979; 31079</t>
+          <t>13589; 31418</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8457; 21657</t>
+          <t>9409; 23850</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11010; 23480</t>
+          <t>11303; 23417</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15850; 31020</t>
+          <t>15460; 31366</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16813; 34343</t>
+          <t>16807; 34566</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13970; 27175</t>
+          <t>17415; 33554</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27406; 46368</t>
+          <t>26569; 46546</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38919; 63705</t>
+          <t>38138; 62278</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35490; 59615</t>
+          <t>34919; 58488</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26101; 45912</t>
+          <t>30878; 51555</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>7782</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>10931</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1901; 5527</t>
+          <t>1570; 5527</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1828; 6016</t>
+          <t>970; 6016</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>965; 5570</t>
+          <t>963; 5570</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 6064</t>
+          <t>0; 5989</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7959; 20647</t>
+          <t>8758; 20960</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16923; 32945</t>
+          <t>16638; 32531</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12581; 26012</t>
+          <t>12217; 26335</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3069; 12715</t>
+          <t>4091; 13323</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12272; 25369</t>
+          <t>12225; 24931</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20187; 36647</t>
+          <t>20451; 37552</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14824; 28846</t>
+          <t>15111; 29639</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4885; 16059</t>
+          <t>6088; 17092</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>333841</t>
+          <t>98886</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>87565</t>
+          <t>96772</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>421406</t>
+          <t>195659</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>124325; 166548</t>
+          <t>124346; 165103</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>195806; 249507</t>
+          <t>197477; 249396</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>139744; 186942</t>
+          <t>142331; 187264</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>119389; 603474</t>
+          <t>80732; 119978</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>78185; 108434</t>
+          <t>79418; 109802</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>122091; 160725</t>
+          <t>122463; 163611</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>101063; 139814</t>
+          <t>102314; 139474</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>73546; 102700</t>
+          <t>80964; 113301</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>216440; 265048</t>
+          <t>212903; 266568</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>329759; 396296</t>
+          <t>328652; 393401</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>255431; 312497</t>
+          <t>255815; 315177</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>213894; 813716</t>
+          <t>171658; 221040</t>
         </is>
       </c>
     </row>
